--- a/Dashboard Tech.xlsx
+++ b/Dashboard Tech.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Win 10\Desktop\Data  Analyst\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17D1F644-AB58-44DA-BBE7-8A9F754DEDAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC73F3A4-B49B-46D5-93F2-7C86781B4897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{82EC9897-DB68-419D-91BC-22E100CEBFA5}"/>
   </bookViews>
@@ -18,8 +18,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="18" r:id="rId3"/>
-    <pivotCache cacheId="62" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="1" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="27">
   <si>
     <t>Date</t>
   </si>
@@ -105,12 +105,31 @@
   <si>
     <t>Sum of Revenue</t>
   </si>
+  <si>
+    <t>Laptops generated the highest revenue at $64,800, accounting for nearly 65% of total sales.</t>
+  </si>
+  <si>
+    <t>INSIGHT  1</t>
+  </si>
+  <si>
+    <t>INSIGHT 2</t>
+  </si>
+  <si>
+    <t>Daily revenue shows an upward trend from January to 
+February, with peak sales on February 20 ($10,400).</t>
+  </si>
+  <si>
+    <t>INSIGHT 3</t>
+  </si>
+  <si>
+    <t>Electronics category dominated with approximately  82.3% of total revenue compared to 17.7% for Furniture.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,6 +144,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFEB5757"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -227,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -241,7 +266,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -260,7 +285,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1561,6 +1603,7 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:numFmt formatCode="0.0%" sourceLinked="0"/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -1605,7 +1648,7 @@
         <c:idx val="1"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent2"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -1622,6 +1665,7 @@
               <c:y val="5.0747302420530768E-3"/>
             </c:manualLayout>
           </c:layout>
+          <c:numFmt formatCode="0.0%" sourceLinked="0"/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -1683,6 +1727,7 @@
               <c:y val="-0.47097440944881891"/>
             </c:manualLayout>
           </c:layout>
+          <c:numFmt formatCode="0.0%" sourceLinked="0"/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -1825,6 +1870,7 @@
                 </c:ext>
               </c:extLst>
             </c:dLbl>
+            <c:numFmt formatCode="0.0%" sourceLinked="0"/>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -3691,13 +3737,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>4762</xdr:rowOff>
+      <xdr:rowOff>72798</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>80962</xdr:rowOff>
+      <xdr:rowOff>148998</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3724,16 +3770,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>163284</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>83004</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>166688</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>465363</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>30617</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3762,16 +3808,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>185737</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>966107</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>8844</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>71437</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>859971</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>85044</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5164,7 +5210,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{84072AA8-D0C4-49E5-B497-A15E2EE7C682}" name="PivotTable21" cacheId="62" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{84072AA8-D0C4-49E5-B497-A15E2EE7C682}" name="PivotTable21" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A18:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField numFmtId="14" showAll="0"/>
@@ -5248,7 +5294,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F74F55CE-C014-439A-9981-52DF6DE43AEC}" name="PivotTable1" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F74F55CE-C014-439A-9981-52DF6DE43AEC}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A1:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0">
@@ -6113,7 +6159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F8C1D3-A2E0-4615-8958-B43BEF12BD29}">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:AF30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -6130,7 +6176,7 @@
     <col min="12" max="12" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>17</v>
       </c>
@@ -6138,93 +6184,186 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2">
         <v>64800</v>
       </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3">
         <v>12600</v>
       </c>
+      <c r="L3" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4">
         <v>8100</v>
       </c>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
+      <c r="S4" s="12"/>
+      <c r="T4" s="12"/>
+      <c r="U4" s="12"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5">
         <v>6525</v>
       </c>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6">
         <v>6450</v>
       </c>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7">
         <v>4375</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8">
         <v>3900</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9">
         <v>2700</v>
       </c>
+      <c r="V9" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10">
         <v>2560</v>
       </c>
+      <c r="V10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="W10" s="16"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="16"/>
+      <c r="Z10" s="16"/>
+      <c r="AA10" s="16"/>
+      <c r="AB10" s="16"/>
+      <c r="AC10" s="16"/>
+      <c r="AD10" s="16"/>
+      <c r="AE10" s="16"/>
+      <c r="AF10" s="16"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="12"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="16"/>
+      <c r="X11" s="16"/>
+      <c r="Y11" s="16"/>
+      <c r="Z11" s="16"/>
+      <c r="AA11" s="16"/>
+      <c r="AB11" s="16"/>
+      <c r="AC11" s="16"/>
+      <c r="AD11" s="16"/>
+      <c r="AE11" s="16"/>
+      <c r="AF11" s="16"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12">
         <v>112010</v>
       </c>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
+      <c r="Z12" s="16"/>
+      <c r="AA12" s="16"/>
+      <c r="AB12" s="16"/>
+      <c r="AC12" s="16"/>
+      <c r="AD12" s="16"/>
+      <c r="AE12" s="16"/>
+      <c r="AF12" s="16"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="V13" s="13"/>
+      <c r="W13" s="13"/>
+      <c r="X13" s="13"/>
+      <c r="Y13" s="13"/>
+      <c r="Z13" s="13"/>
+      <c r="AA13" s="13"/>
+      <c r="AB13" s="13"/>
+      <c r="AC13" s="13"/>
+      <c r="AD13" s="13"/>
+      <c r="AE13" s="13"/>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AA17" s="14"/>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>17</v>
       </c>
@@ -6232,33 +6371,98 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19">
         <v>92200</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20">
         <v>19810</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21">
         <v>112010</v>
       </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="J26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="J27" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15"/>
+      <c r="R27" s="15"/>
+      <c r="S27" s="15"/>
+      <c r="T27" s="15"/>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="15"/>
+      <c r="R28" s="15"/>
+      <c r="S28" s="15"/>
+      <c r="T28" s="15"/>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="17"/>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="17"/>
+      <c r="S30" s="17"/>
+      <c r="T30" s="17"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="V10:AF12"/>
+    <mergeCell ref="J27:T28"/>
+    <mergeCell ref="L3:U4"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
